--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3852" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{369CDB6C-3AB0-4740-8ADE-8E75C213342C}"/>
+  <xr:revisionPtr revIDLastSave="3929" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{244BBF0A-1309-4400-8D82-23588023FE0C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$GS$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Collection Detail'!$A$2:$AF$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$CP$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$F$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="165">
   <si>
     <t>Clients</t>
   </si>
@@ -532,6 +532,15 @@
   </si>
   <si>
     <t>TARA</t>
+  </si>
+  <si>
+    <t>Jyoti Sarwan</t>
+  </si>
+  <si>
+    <t>Subu</t>
+  </si>
+  <si>
+    <t>Satya</t>
   </si>
 </sst>
 </file>
@@ -1794,8 +1803,8 @@
       <c r="C4" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>84</v>
+      <c r="D4" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>107</v>
@@ -3467,7 +3476,7 @@
         <v>145</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>107</v>
@@ -3669,10 +3678,10 @@
         <v>161</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>107</v>
@@ -4080,7 +4089,7 @@
         <v>142</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>107</v>
@@ -4481,7 +4490,7 @@
         <v>160</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>153</v>
@@ -4567,14 +4576,14 @@
         <v>360</v>
       </c>
       <c r="AK17" s="3">
-        <v>360</v>
+        <v>485</v>
       </c>
       <c r="AL17" s="3">
-        <v>92.268749003049038</v>
+        <v>217.26874900304904</v>
       </c>
       <c r="AM17" s="4">
         <f t="shared" si="8"/>
-        <v>0.25630208056402509</v>
+        <v>0.44797680206814233</v>
       </c>
       <c r="AN17" s="3">
         <v>103278.92877848257</v>
@@ -4595,14 +4604,14 @@
         <v>390</v>
       </c>
       <c r="AY17" s="17">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="AZ17" s="17">
-        <v>122.26874900304904</v>
+        <v>152</v>
       </c>
       <c r="BA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.31350961282833084</v>
+        <v>0.3619047619047619</v>
       </c>
       <c r="BB17" s="3">
         <v>103278.92877848257</v>
@@ -4626,15 +4635,15 @@
       </c>
       <c r="BM17" s="17">
         <f t="shared" si="2"/>
-        <v>1583.1275323</v>
+        <v>1738.1275323</v>
       </c>
       <c r="BN17" s="17">
         <f t="shared" si="3"/>
-        <v>541.66124922373388</v>
+        <v>696.39250022068484</v>
       </c>
       <c r="BO17" s="4">
         <f t="shared" si="11"/>
-        <v>0.34214631365598031</v>
+        <v>0.40065673391593676</v>
       </c>
       <c r="BP17" s="3">
         <f t="shared" si="4"/>
@@ -4689,10 +4698,10 @@
         <v>160</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>107</v>
@@ -4893,10 +4902,10 @@
         <v>161</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>107</v>
@@ -5727,7 +5736,7 @@
         <v>146</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>107</v>
@@ -5938,7 +5947,7 @@
         <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>127</v>
@@ -6568,7 +6577,7 @@
         <v>146</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>107</v>
@@ -7185,7 +7194,7 @@
         <v>142</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>107</v>
@@ -8817,7 +8826,7 @@
         <v>161</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>150</v>
@@ -9439,7 +9448,7 @@
         <v>142</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E41" s="26" t="s">
         <v>107</v>
@@ -9841,7 +9850,7 @@
         <v>146</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>107</v>
@@ -10043,7 +10052,7 @@
         <v>146</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>107</v>
@@ -11712,7 +11721,7 @@
         <v>142</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E52" s="26" t="s">
         <v>107</v>
@@ -11914,7 +11923,7 @@
         <v>142</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E53" s="26" t="s">
         <v>107</v>
@@ -12116,7 +12125,7 @@
         <v>146</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>107</v>
@@ -12315,7 +12324,7 @@
         <v>161</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>127</v>
@@ -12520,7 +12529,7 @@
         <v>161</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>127</v>
@@ -13064,7 +13073,7 @@
       <c r="C59" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D59" s="16" t="s">
+      <c r="D59" s="3" t="s">
         <v>83</v>
       </c>
       <c r="E59" s="25" t="s">
@@ -13260,7 +13269,7 @@
       <c r="C60" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="3" t="s">
         <v>83</v>
       </c>
       <c r="E60" s="25" t="s">
@@ -13586,11 +13595,11 @@
       <c r="B62" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>107</v>
@@ -13698,7 +13707,7 @@
         <v>146</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>108</v>
@@ -35027,11 +35036,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="H1:U1"/>
-    <mergeCell ref="W1:AJ1"/>
-    <mergeCell ref="AL1:AY1"/>
-    <mergeCell ref="BA1:BN1"/>
-    <mergeCell ref="BP1:CC1"/>
     <mergeCell ref="FB1:FO1"/>
     <mergeCell ref="FQ1:GD1"/>
     <mergeCell ref="GF1:GS1"/>
@@ -35040,6 +35044,11 @@
     <mergeCell ref="DI1:DV1"/>
     <mergeCell ref="DX1:EK1"/>
     <mergeCell ref="EM1:EZ1"/>
+    <mergeCell ref="H1:U1"/>
+    <mergeCell ref="W1:AJ1"/>
+    <mergeCell ref="AL1:AY1"/>
+    <mergeCell ref="BA1:BN1"/>
+    <mergeCell ref="BP1:CC1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:B64">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -35036,6 +35036,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="H1:U1"/>
+    <mergeCell ref="W1:AJ1"/>
+    <mergeCell ref="AL1:AY1"/>
+    <mergeCell ref="BA1:BN1"/>
+    <mergeCell ref="BP1:CC1"/>
     <mergeCell ref="FB1:FO1"/>
     <mergeCell ref="FQ1:GD1"/>
     <mergeCell ref="GF1:GS1"/>
@@ -35044,11 +35049,6 @@
     <mergeCell ref="DI1:DV1"/>
     <mergeCell ref="DX1:EK1"/>
     <mergeCell ref="EM1:EZ1"/>
-    <mergeCell ref="H1:U1"/>
-    <mergeCell ref="W1:AJ1"/>
-    <mergeCell ref="AL1:AY1"/>
-    <mergeCell ref="BA1:BN1"/>
-    <mergeCell ref="BP1:CC1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:B64">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3976" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{723FF7F0-51BE-4C18-82D2-422BB1BBA77F}"/>
+  <xr:revisionPtr revIDLastSave="4009" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7075132-3E3F-43A7-96CE-BDBA9213142D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="Collection Detail" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$GS$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Collection Detail'!$A$2:$AF$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$F$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Collection Detail'!$A$2:$F$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$CP$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -4472,10 +4472,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>151</v>
@@ -12306,10 +12306,10 @@
         <v>65</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>125</v>
@@ -12511,10 +12511,10 @@
         <v>120</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>125</v>
@@ -19312,10 +19312,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>151</v>
@@ -19645,7 +19645,7 @@
         <v>156</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>151</v>
@@ -31816,10 +31816,10 @@
         <v>65</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>125</v>
@@ -32144,10 +32144,10 @@
         <v>120</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>125</v>
@@ -35715,10 +35715,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>151</v>
@@ -35756,7 +35756,7 @@
         <v>156</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>151</v>
@@ -37159,10 +37159,10 @@
         <v>65</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>125</v>
@@ -37197,10 +37197,10 @@
         <v>120</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>125</v>

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4009" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7075132-3E3F-43A7-96CE-BDBA9213142D}"/>
+  <xr:revisionPtr revIDLastSave="4018" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{091CACB0-5A15-4E95-905F-F25101156AC3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -791,6 +791,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -804,9 +807,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1217,86 +1217,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.35">
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="V1" s="40" t="s">
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="V1" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AJ1" s="38" t="s">
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
+      <c r="AD1" s="42"/>
+      <c r="AE1" s="42"/>
+      <c r="AF1" s="42"/>
+      <c r="AG1" s="42"/>
+      <c r="AH1" s="42"/>
+      <c r="AJ1" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="39"/>
-      <c r="AM1" s="39"/>
-      <c r="AN1" s="39"/>
-      <c r="AO1" s="39"/>
-      <c r="AP1" s="39"/>
-      <c r="AQ1" s="39"/>
-      <c r="AR1" s="39"/>
-      <c r="AS1" s="39"/>
-      <c r="AT1" s="39"/>
-      <c r="AU1" s="39"/>
-      <c r="AV1" s="39"/>
-      <c r="AX1" s="40" t="s">
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
+      <c r="AQ1" s="40"/>
+      <c r="AR1" s="40"/>
+      <c r="AS1" s="40"/>
+      <c r="AT1" s="40"/>
+      <c r="AU1" s="40"/>
+      <c r="AV1" s="40"/>
+      <c r="AX1" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="AY1" s="41"/>
-      <c r="AZ1" s="41"/>
-      <c r="BA1" s="41"/>
-      <c r="BB1" s="41"/>
-      <c r="BC1" s="41"/>
-      <c r="BD1" s="41"/>
-      <c r="BE1" s="41"/>
-      <c r="BF1" s="41"/>
-      <c r="BG1" s="41"/>
-      <c r="BH1" s="41"/>
-      <c r="BI1" s="41"/>
-      <c r="BJ1" s="41"/>
-      <c r="BL1" s="39" t="s">
+      <c r="AY1" s="42"/>
+      <c r="AZ1" s="42"/>
+      <c r="BA1" s="42"/>
+      <c r="BB1" s="42"/>
+      <c r="BC1" s="42"/>
+      <c r="BD1" s="42"/>
+      <c r="BE1" s="42"/>
+      <c r="BF1" s="42"/>
+      <c r="BG1" s="42"/>
+      <c r="BH1" s="42"/>
+      <c r="BI1" s="42"/>
+      <c r="BJ1" s="42"/>
+      <c r="BL1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="BM1" s="39"/>
-      <c r="BN1" s="39"/>
-      <c r="BO1" s="39"/>
-      <c r="BP1" s="39"/>
-      <c r="BQ1" s="39"/>
-      <c r="BR1" s="39"/>
-      <c r="BS1" s="39"/>
-      <c r="BT1" s="39"/>
-      <c r="BU1" s="39"/>
-      <c r="BV1" s="39"/>
-      <c r="BW1" s="39"/>
-      <c r="BX1" s="39"/>
-      <c r="BZ1" s="37" t="s">
+      <c r="BM1" s="40"/>
+      <c r="BN1" s="40"/>
+      <c r="BO1" s="40"/>
+      <c r="BP1" s="40"/>
+      <c r="BQ1" s="40"/>
+      <c r="BR1" s="40"/>
+      <c r="BS1" s="40"/>
+      <c r="BT1" s="40"/>
+      <c r="BU1" s="40"/>
+      <c r="BV1" s="40"/>
+      <c r="BW1" s="40"/>
+      <c r="BX1" s="40"/>
+      <c r="BZ1" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="CA1" s="37"/>
-      <c r="CB1" s="37"/>
+      <c r="CA1" s="38"/>
+      <c r="CB1" s="38"/>
       <c r="CD1" s="19" t="s">
         <v>78</v>
       </c>
@@ -2051,14 +2051,14 @@
         <v>24</v>
       </c>
       <c r="W5" s="7">
-        <v>24</v>
+        <v>18.504999999999999</v>
       </c>
       <c r="X5" s="3">
         <v>7.1946064492771349</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="7"/>
-        <v>0.29977526871988064</v>
+        <v>0.38879256683475466</v>
       </c>
       <c r="Z5" s="3">
         <v>111064.27936574571</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="BM5" s="17">
         <f t="shared" si="2"/>
-        <v>79.254676599999996</v>
+        <v>73.759676599999992</v>
       </c>
       <c r="BN5" s="17">
         <f t="shared" si="3"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="BO5" s="4">
         <f t="shared" si="11"/>
-        <v>0.16075696635738079</v>
+        <v>0.17273315132527706</v>
       </c>
       <c r="BP5" s="3">
         <f t="shared" si="4"/>
@@ -2258,14 +2258,14 @@
         <v>63</v>
       </c>
       <c r="W6" s="7">
-        <v>63</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="X6" s="3">
         <v>4.1018832792274864</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="7"/>
-        <v>6.5109258400436298E-2</v>
+        <v>6.2719927816934043E-2</v>
       </c>
       <c r="Z6" s="3">
         <v>121638.60335929081</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="BM6" s="17">
         <f t="shared" si="2"/>
-        <v>245.4</v>
+        <v>247.8</v>
       </c>
       <c r="BN6" s="17">
         <f t="shared" si="3"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="BO6" s="4">
         <f t="shared" si="11"/>
-        <v>5.962788618917355E-2</v>
+        <v>5.9050376395573805E-2</v>
       </c>
       <c r="BP6" s="3">
         <f t="shared" si="4"/>
@@ -2889,14 +2889,14 @@
         <v>45.5</v>
       </c>
       <c r="W9" s="7">
-        <v>42.75</v>
+        <v>42.25</v>
       </c>
       <c r="X9" s="3">
         <v>7.9225720575444001</v>
       </c>
       <c r="Y9" s="4">
         <f t="shared" si="7"/>
-        <v>0.18532332298349474</v>
+        <v>0.18751649840341775</v>
       </c>
       <c r="Z9" s="3">
         <v>88198.705860335351</v>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BM9" s="17">
         <f t="shared" si="2"/>
-        <v>164.27500000000001</v>
+        <v>163.77500000000001</v>
       </c>
       <c r="BN9" s="17">
         <f t="shared" si="3"/>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="BO9" s="4">
         <f t="shared" si="11"/>
-        <v>0.19414955442094189</v>
+        <v>0.19474228699435342</v>
       </c>
       <c r="BP9" s="3">
         <f t="shared" si="4"/>
@@ -3100,14 +3100,14 @@
         <v>12</v>
       </c>
       <c r="W10" s="7">
-        <v>11.21</v>
+        <v>9.3286154000000003</v>
       </c>
       <c r="X10" s="3">
         <v>2.6859121366836085</v>
       </c>
       <c r="Y10" s="4">
         <f t="shared" si="7"/>
-        <v>0.23959965536874295</v>
+        <v>0.28792184279390576</v>
       </c>
       <c r="Z10" s="3">
         <v>115950.98592417133</v>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="BM10" s="17">
         <f t="shared" si="2"/>
-        <v>48.230519100000002</v>
+        <v>46.349134500000005</v>
       </c>
       <c r="BN10" s="17">
         <f t="shared" si="3"/>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="BO10" s="4">
         <f t="shared" si="11"/>
-        <v>0.30457590698066134</v>
+        <v>0.31693912426845017</v>
       </c>
       <c r="BP10" s="3">
         <f t="shared" si="4"/>
@@ -3308,14 +3308,14 @@
         <v>47.199999999999996</v>
       </c>
       <c r="W11" s="7">
-        <v>40.6</v>
+        <v>42.125250000000001</v>
       </c>
       <c r="X11" s="3">
         <v>8.6905081391468855</v>
       </c>
       <c r="Y11" s="4">
         <f t="shared" si="7"/>
-        <v>0.21405192460952918</v>
+        <v>0.20630163949524064</v>
       </c>
       <c r="Z11" s="3">
         <v>101782.68220545011</v>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="BM11" s="17">
         <f t="shared" si="2"/>
-        <v>169.85</v>
+        <v>171.37524999999999</v>
       </c>
       <c r="BN11" s="17">
         <f t="shared" si="3"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="BO11" s="4">
         <f t="shared" si="11"/>
-        <v>0.25228061346363628</v>
+        <v>0.25003530087803594</v>
       </c>
       <c r="BP11" s="3">
         <f t="shared" si="4"/>
@@ -3721,14 +3721,14 @@
         <v>27</v>
       </c>
       <c r="W13" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13" s="3">
         <v>-6.7076312492347991</v>
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="7"/>
-        <v>-0.83845390615434989</v>
+        <v>-0.74529236102608876</v>
       </c>
       <c r="Z13" s="3">
         <v>140662.332309839</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BM13" s="17">
         <f t="shared" si="2"/>
-        <v>34.43797</v>
+        <v>35.43797</v>
       </c>
       <c r="BN13" s="17">
         <f t="shared" si="3"/>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="BO13" s="4">
         <f t="shared" si="11"/>
-        <v>-0.75013373686988327</v>
+        <v>-0.72896622256616095</v>
       </c>
       <c r="BP13" s="3">
         <f t="shared" si="4"/>
@@ -5152,14 +5152,14 @@
         <v>24.865000000000002</v>
       </c>
       <c r="W20" s="7">
-        <v>25.19</v>
+        <v>26.69</v>
       </c>
       <c r="X20" s="3">
         <v>7.9281948071674471</v>
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="7"/>
-        <v>0.3147358002051388</v>
+        <v>0.29704738880357612</v>
       </c>
       <c r="Z20" s="3">
         <v>96413.491463351384</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="BM20" s="17">
         <f t="shared" si="2"/>
-        <v>105.4358</v>
+        <v>106.9358</v>
       </c>
       <c r="BN20" s="17">
         <f t="shared" si="3"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="BO20" s="4">
         <f t="shared" si="11"/>
-        <v>0.34790871026014258</v>
+        <v>0.34302855725815246</v>
       </c>
       <c r="BP20" s="3">
         <f t="shared" si="4"/>
@@ -5363,14 +5363,14 @@
         <v>90</v>
       </c>
       <c r="W21" s="7">
-        <v>73.14</v>
+        <v>109.7276</v>
       </c>
       <c r="X21" s="3">
         <v>-46.737419372020142</v>
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="7"/>
-        <v>-0.63901311692671781</v>
+        <v>-0.42594041400723376</v>
       </c>
       <c r="Z21" s="3">
         <v>101866.14273796191</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="BM21" s="17">
         <f t="shared" si="2"/>
-        <v>377.78298274999997</v>
+        <v>414.37058275000004</v>
       </c>
       <c r="BN21" s="17">
         <f t="shared" si="3"/>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="BO21" s="4">
         <f t="shared" si="11"/>
-        <v>-0.26113260231690089</v>
+        <v>-0.23807542693267686</v>
       </c>
       <c r="BP21" s="3">
         <f t="shared" si="4"/>
@@ -5569,14 +5569,14 @@
         <v>23</v>
       </c>
       <c r="W22" s="7">
-        <v>13.23</v>
+        <v>12.16</v>
       </c>
       <c r="X22" s="3">
         <v>11.003353524046769</v>
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="7"/>
-        <v>0.83169716735047383</v>
+        <v>0.9048810463854251</v>
       </c>
       <c r="Z22" s="3">
         <v>113394.03349761825</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="BM22" s="17">
         <f t="shared" si="2"/>
-        <v>67.490000000000009</v>
+        <v>66.42</v>
       </c>
       <c r="BN22" s="17">
         <f t="shared" si="3"/>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="BO22" s="4">
         <f t="shared" si="11"/>
-        <v>0.90102327118299452</v>
+        <v>0.91553840066456349</v>
       </c>
       <c r="BP22" s="3">
         <f t="shared" si="4"/>
@@ -5776,14 +5776,14 @@
         <v>4</v>
       </c>
       <c r="W23" s="7">
-        <v>2.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="X23" s="3">
         <v>-0.11884456849450231</v>
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="7"/>
-        <v>-4.7537827397800922E-2</v>
+        <v>-5.1671551519348838E-2</v>
       </c>
       <c r="Z23" s="3">
         <v>121160.29442970302</v>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="BM23" s="17">
         <f t="shared" si="2"/>
-        <v>4.8909400000000005</v>
+        <v>4.6909399999999994</v>
       </c>
       <c r="BN23" s="17">
         <f t="shared" si="3"/>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="BO23" s="4">
         <f t="shared" si="11"/>
-        <v>-1.2673913701802335</v>
+        <v>-1.3214270803014563</v>
       </c>
       <c r="BP23" s="3">
         <f t="shared" si="4"/>
@@ -5990,14 +5990,14 @@
         <v>29</v>
       </c>
       <c r="W24" s="7">
-        <v>22.5</v>
+        <v>21</v>
       </c>
       <c r="X24" s="3">
         <v>0.66834942117908014</v>
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="7"/>
-        <v>2.9704418719070227E-2</v>
+        <v>3.1826162913289532E-2</v>
       </c>
       <c r="Z24" s="3">
         <v>110922.19210275145</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="BM24" s="17">
         <f t="shared" si="2"/>
-        <v>82.400570000000002</v>
+        <v>80.900570000000002</v>
       </c>
       <c r="BN24" s="17">
         <f t="shared" si="3"/>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="BO24" s="4">
         <f t="shared" si="11"/>
-        <v>-3.6487199577518295E-2</v>
+        <v>-3.7163718906940542E-2</v>
       </c>
       <c r="BP24" s="3">
         <f t="shared" si="4"/>
@@ -6409,14 +6409,14 @@
         <v>48</v>
       </c>
       <c r="W26" s="7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="X26" s="3">
         <v>-24.18199956970426</v>
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="7"/>
-        <v>-0.50379165770217205</v>
+        <v>-0.40303332616173765</v>
       </c>
       <c r="Z26" s="3">
         <v>128852.65163945478</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="BM26" s="17">
         <f t="shared" si="2"/>
-        <v>240.05248</v>
+        <v>252.05248</v>
       </c>
       <c r="BN26" s="17">
         <f t="shared" si="3"/>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="BO26" s="4">
         <f t="shared" si="11"/>
-        <v>-0.23725256510278464</v>
+        <v>-0.22595717621697237</v>
       </c>
       <c r="BP26" s="3">
         <f t="shared" si="4"/>
@@ -6615,14 +6615,14 @@
         <v>4</v>
       </c>
       <c r="W27" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X27" s="3">
         <v>1.5644221688453399</v>
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="7"/>
-        <v>0.52147405628178001</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="3">
         <v>143349.27507898747</v>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="BM27" s="17">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BN27" s="17">
         <f t="shared" si="3"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="BO27" s="4">
         <f t="shared" si="11"/>
-        <v>0.28221108442266996</v>
+        <v>0.56442216884533991</v>
       </c>
       <c r="BP27" s="3">
         <f t="shared" si="4"/>
@@ -6819,14 +6819,14 @@
         <v>50</v>
       </c>
       <c r="W28" s="7">
-        <v>50</v>
+        <v>53.9</v>
       </c>
       <c r="X28" s="3">
         <v>15.262871531248564</v>
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="7"/>
-        <v>0.30525743062497129</v>
+        <v>0.28317015827919412</v>
       </c>
       <c r="Z28" s="3">
         <v>91610.207494955641</v>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="BM28" s="17">
         <f t="shared" si="2"/>
-        <v>179.69</v>
+        <v>183.59</v>
       </c>
       <c r="BN28" s="17">
         <f t="shared" si="3"/>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="BO28" s="4">
         <f t="shared" si="11"/>
-        <v>0.23548447112272466</v>
+        <v>0.23048207754258074</v>
       </c>
       <c r="BP28" s="3">
         <f t="shared" si="4"/>
@@ -7023,14 +7023,14 @@
         <v>16</v>
       </c>
       <c r="W29" s="7">
-        <v>21.375999999999998</v>
+        <v>24.708280000000002</v>
       </c>
       <c r="X29" s="3">
         <v>-9.0913462557081779</v>
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="7"/>
-        <v>-0.42530624324982125</v>
+        <v>-0.36794735431637399</v>
       </c>
       <c r="Z29" s="3">
         <v>100930.86921463661</v>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="BM29" s="17">
         <f t="shared" si="2"/>
-        <v>92.026710000000008</v>
+        <v>95.358990000000006</v>
       </c>
       <c r="BN29" s="17">
         <f t="shared" si="3"/>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="BO29" s="4">
         <f t="shared" si="11"/>
-        <v>-0.20837291810618069</v>
+        <v>-0.20109141368224687</v>
       </c>
       <c r="BP29" s="3">
         <f t="shared" si="4"/>
@@ -7232,14 +7232,14 @@
         <v>3</v>
       </c>
       <c r="W30" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X30" s="3">
         <v>3.8119999999999998</v>
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="7"/>
-        <v>0.76239999999999997</v>
+        <v>1.2706666666666666</v>
       </c>
       <c r="Z30" s="3">
         <v>121000.00000000001</v>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="BM30" s="17">
         <f t="shared" si="2"/>
-        <v>10.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="BN30" s="17">
         <f t="shared" si="3"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="BO30" s="4">
         <f t="shared" si="11"/>
-        <v>0.66999999999999993</v>
+        <v>0.82227272727272716</v>
       </c>
       <c r="BP30" s="3">
         <f t="shared" si="4"/>
@@ -7640,14 +7640,14 @@
         <v>63.39</v>
       </c>
       <c r="W32" s="7">
-        <v>63.379999999999995</v>
+        <v>68.03</v>
       </c>
       <c r="X32" s="3">
         <v>20.38111859595562</v>
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="7"/>
-        <v>0.32157018927036324</v>
+        <v>0.29959016016398088</v>
       </c>
       <c r="Z32" s="3">
         <v>96744.027529400701</v>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM32" s="17">
         <f t="shared" si="2"/>
-        <v>264.66999999999996</v>
+        <v>269.32</v>
       </c>
       <c r="BN32" s="17">
         <f t="shared" si="3"/>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="BO32" s="4">
         <f t="shared" si="11"/>
-        <v>0.36442763105250753</v>
+        <v>0.35813553063518178</v>
       </c>
       <c r="BP32" s="3">
         <f t="shared" si="4"/>
@@ -8257,14 +8257,14 @@
         <v>9.1</v>
       </c>
       <c r="W35" s="7">
-        <v>9.1</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="X35" s="3">
         <v>1.7797095810564079</v>
       </c>
       <c r="Y35" s="4">
         <f t="shared" si="7"/>
-        <v>0.1955724814347701</v>
+        <v>0.18013254868991982</v>
       </c>
       <c r="Z35" s="3">
         <v>104721.45808715979</v>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="BM35" s="17">
         <f t="shared" ref="BM35:BM55" si="15">W35+AK35+AY35+I35</f>
-        <v>41.01</v>
+        <v>41.79</v>
       </c>
       <c r="BN35" s="17">
         <f t="shared" ref="BN35:BN55" si="16">X35+AL35+AZ35+J35</f>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="BO35" s="4">
         <f t="shared" si="11"/>
-        <v>0.32140524688505362</v>
+        <v>0.31540629755338717</v>
       </c>
       <c r="BP35" s="3">
         <f t="shared" ref="BP35:BP63" si="17">AVERAGE(L35,Z35,AN35,BB35)</f>
@@ -8461,14 +8461,14 @@
         <v>24.713999999999999</v>
       </c>
       <c r="W36" s="7">
-        <v>19.68</v>
+        <v>20.447670000000002</v>
       </c>
       <c r="X36" s="3">
         <v>7.6712019897435795</v>
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="7"/>
-        <v>0.38979684907233636</v>
+        <v>0.37516264639167096</v>
       </c>
       <c r="Z36" s="3">
         <v>90583.505565571017</v>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="BM36" s="17">
         <f t="shared" si="15"/>
-        <v>84.834104999999994</v>
+        <v>85.601775000000004</v>
       </c>
       <c r="BN36" s="17">
         <f t="shared" si="16"/>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="BO36" s="4">
         <f t="shared" si="11"/>
-        <v>0.44047236580833671</v>
+        <v>0.43652224420092739</v>
       </c>
       <c r="BP36" s="3">
         <f t="shared" si="17"/>
@@ -8869,14 +8869,14 @@
         <v>64</v>
       </c>
       <c r="W38" s="7">
-        <v>25</v>
+        <v>32.1</v>
       </c>
       <c r="X38" s="3">
         <v>-19.859391554768017</v>
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="7"/>
-        <v>-0.79437566219072064</v>
+        <v>-0.61867263410492257</v>
       </c>
       <c r="Z38" s="3">
         <v>110681.37839052675</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BM38" s="17">
         <f t="shared" si="15"/>
-        <v>126.4045</v>
+        <v>133.50450000000001</v>
       </c>
       <c r="BN38" s="17">
         <f t="shared" si="16"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="BO38" s="4">
         <f t="shared" si="11"/>
-        <v>-0.42470856322360917</v>
+        <v>-0.40212182795335516</v>
       </c>
       <c r="BP38" s="3">
         <f t="shared" si="17"/>
@@ -9076,14 +9076,14 @@
         <v>18</v>
       </c>
       <c r="W39" s="7">
-        <v>8.6300000000000008</v>
+        <v>13.68</v>
       </c>
       <c r="X39" s="3">
         <v>-2.0652687961694376</v>
       </c>
       <c r="Y39" s="4">
         <f t="shared" si="7"/>
-        <v>-0.23931272261523029</v>
+        <v>-0.15096994124045596</v>
       </c>
       <c r="Z39" s="3">
         <v>102820.3358502386</v>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="BM39" s="17">
         <f t="shared" si="15"/>
-        <v>58.204030000000003</v>
+        <v>63.25403</v>
       </c>
       <c r="BN39" s="17">
         <f t="shared" si="16"/>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="BO39" s="4">
         <f t="shared" si="11"/>
-        <v>0.27603203912336283</v>
+        <v>0.25399452155218227</v>
       </c>
       <c r="BP39" s="3">
         <f t="shared" si="17"/>
@@ -9280,14 +9280,14 @@
         <v>16</v>
       </c>
       <c r="W40" s="7">
-        <v>16</v>
+        <v>16.114850000000001</v>
       </c>
       <c r="X40" s="3">
         <v>3.0799649275377785</v>
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="7"/>
-        <v>0.19249780797111116</v>
+        <v>0.19112588249582083</v>
       </c>
       <c r="Z40" s="3">
         <v>113178.34248072768</v>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="BM40" s="17">
         <f t="shared" si="15"/>
-        <v>62.866760400000004</v>
+        <v>62.981610400000008</v>
       </c>
       <c r="BN40" s="17">
         <f t="shared" si="16"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="BO40" s="4">
         <f t="shared" si="11"/>
-        <v>0.21391020755967541</v>
+        <v>0.21352013199345538</v>
       </c>
       <c r="BP40" s="3">
         <f t="shared" si="17"/>
@@ -9686,14 +9686,14 @@
         <v>28.5</v>
       </c>
       <c r="W42" s="7">
-        <v>28.5</v>
+        <v>28.95</v>
       </c>
       <c r="X42" s="3">
         <v>10.290401339084465</v>
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="7"/>
-        <v>0.36106671365208648</v>
+        <v>0.35545427768858257</v>
       </c>
       <c r="Z42" s="3">
         <v>120092.31438033683</v>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="BM42" s="17">
         <f t="shared" si="15"/>
-        <v>106.61</v>
+        <v>107.06</v>
       </c>
       <c r="BN42" s="17">
         <f t="shared" si="16"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BO42" s="4">
         <f t="shared" si="11"/>
-        <v>0.34071272998120616</v>
+        <v>0.33928062902387807</v>
       </c>
       <c r="BP42" s="3">
         <f t="shared" si="17"/>
@@ -9888,14 +9888,14 @@
         <v>0</v>
       </c>
       <c r="W43" s="7">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="X43" s="3">
         <v>-2.6817886394136181E-2</v>
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="7"/>
-        <v>-8.9392954647120604E-3</v>
+        <v>-1.48988257745201E-2</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="BM43" s="17">
         <f t="shared" si="15"/>
-        <v>5.4180000000000001</v>
+        <v>4.218</v>
       </c>
       <c r="BN43" s="17">
         <f t="shared" si="16"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="BO43" s="4">
         <f t="shared" si="11"/>
-        <v>-0.17216957508150493</v>
+        <v>-0.2211509620179217</v>
       </c>
       <c r="BP43" s="3">
         <f t="shared" si="17"/>
@@ -10092,14 +10092,14 @@
         <v>20</v>
       </c>
       <c r="W44" s="7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X44" s="3">
         <v>2.2581580118894564</v>
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="7"/>
-        <v>0.11290790059447282</v>
+        <v>0.10264354599497529</v>
       </c>
       <c r="Z44" s="3">
         <v>123997.86326418004</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="BM44" s="17">
         <f t="shared" si="15"/>
-        <v>66.912499999999994</v>
+        <v>68.912499999999994</v>
       </c>
       <c r="BN44" s="17">
         <f t="shared" si="16"/>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="BO44" s="4">
         <f t="shared" si="11"/>
-        <v>-1.9489692655538834E-2</v>
+        <v>-1.8924056735914997E-2</v>
       </c>
       <c r="BP44" s="3">
         <f t="shared" si="17"/>
@@ -10306,14 +10306,14 @@
         <v>43.296000000000006</v>
       </c>
       <c r="W45" s="7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="X45" s="3">
         <v>12.210274602624189</v>
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="7"/>
-        <v>0.40700915342080629</v>
+        <v>0.45223239268978477</v>
       </c>
       <c r="Z45" s="3">
         <v>127216.46290564603</v>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="BM45" s="17">
         <f t="shared" si="15"/>
-        <v>136.92000000000002</v>
+        <v>133.92000000000002</v>
       </c>
       <c r="BN45" s="17">
         <f t="shared" si="16"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="BO45" s="4">
         <f t="shared" si="11"/>
-        <v>0.50114951291503695</v>
+        <v>0.51237598049825916</v>
       </c>
       <c r="BP45" s="3">
         <f t="shared" si="17"/>
@@ -10516,14 +10516,14 @@
         <v>20.399999999999999</v>
       </c>
       <c r="W46" s="7">
-        <v>19.940000000000001</v>
+        <v>25.22</v>
       </c>
       <c r="X46" s="3">
         <v>1.5658543529773112</v>
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="7"/>
-        <v>7.8528302556535159E-2</v>
+        <v>6.208780146618998E-2</v>
       </c>
       <c r="Z46" s="3">
         <v>82448.459752116294</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="BM46" s="17">
         <f t="shared" si="15"/>
-        <v>88.375100000000003</v>
+        <v>93.655100000000004</v>
       </c>
       <c r="BN46" s="17">
         <f t="shared" si="16"/>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="BO46" s="4">
         <f t="shared" si="11"/>
-        <v>0.17783818108381252</v>
+        <v>0.16781218574428985</v>
       </c>
       <c r="BP46" s="3">
         <f t="shared" si="17"/>
@@ -10720,14 +10720,14 @@
         <v>12</v>
       </c>
       <c r="W47" s="7">
-        <v>12</v>
+        <v>12.290050000000001</v>
       </c>
       <c r="X47" s="3">
         <v>3.7775750414052212</v>
       </c>
       <c r="Y47" s="4">
         <f t="shared" si="7"/>
-        <v>0.31479792011710178</v>
+        <v>0.30736856574263088</v>
       </c>
       <c r="Z47" s="3">
         <v>119545.75414001002</v>
@@ -10807,7 +10807,7 @@
       </c>
       <c r="BM47" s="17">
         <f t="shared" si="15"/>
-        <v>49.70505</v>
+        <v>49.995100000000001</v>
       </c>
       <c r="BN47" s="17">
         <f t="shared" si="16"/>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="BO47" s="4">
         <f t="shared" si="11"/>
-        <v>0.34479082275837231</v>
+        <v>0.34279049516344667</v>
       </c>
       <c r="BP47" s="3">
         <f t="shared" si="17"/>
@@ -11138,14 +11138,14 @@
         <v>115.69</v>
       </c>
       <c r="W49" s="7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X49" s="3">
         <v>-24.91041467184327</v>
       </c>
       <c r="Y49" s="4">
         <f t="shared" si="7"/>
-        <v>-0.45291663039715035</v>
+        <v>-0.41517357786405451</v>
       </c>
       <c r="Z49" s="3">
         <v>111100.00000000001</v>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="BM49" s="17">
         <f t="shared" si="15"/>
-        <v>365.06658720999997</v>
+        <v>370.06658720999997</v>
       </c>
       <c r="BN49" s="17">
         <f t="shared" si="16"/>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="BO49" s="4">
         <f t="shared" si="11"/>
-        <v>0.18657839633295692</v>
+        <v>0.18405752032332301</v>
       </c>
       <c r="BP49" s="3">
         <f t="shared" si="17"/>
@@ -11759,14 +11759,14 @@
         <v>6</v>
       </c>
       <c r="W52" s="7">
-        <v>9.5</v>
+        <v>12.2</v>
       </c>
       <c r="X52" s="3">
         <v>6.2028212675386794</v>
       </c>
       <c r="Y52" s="4">
         <f t="shared" si="7"/>
-        <v>0.65292855447775577</v>
+        <v>0.50842797274907214</v>
       </c>
       <c r="Z52" s="3">
         <v>153355.57764106497</v>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="BM52" s="17">
         <f t="shared" si="15"/>
-        <v>26.7</v>
+        <v>29.4</v>
       </c>
       <c r="BN52" s="17">
         <f t="shared" si="16"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="BO52" s="4">
         <f t="shared" si="11"/>
-        <v>0.55330218309928936</v>
+        <v>0.50248871730445666</v>
       </c>
       <c r="BP52" s="3">
         <f t="shared" si="17"/>
@@ -12367,14 +12367,14 @@
         <v>130.62295999999998</v>
       </c>
       <c r="W55" s="7">
-        <v>130.60000000000002</v>
+        <v>132</v>
       </c>
       <c r="X55" s="3">
         <v>48.582812270367128</v>
       </c>
       <c r="Y55" s="4">
         <f t="shared" si="7"/>
-        <v>0.37199703116667016</v>
+        <v>0.36805160810884185</v>
       </c>
       <c r="Z55" s="3">
         <v>55820.296406533576</v>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="BM55" s="17">
         <f t="shared" si="15"/>
-        <v>520.88729506000004</v>
+        <v>522.28729506000002</v>
       </c>
       <c r="BN55" s="17">
         <f t="shared" si="16"/>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="BO55" s="4">
         <f t="shared" si="11"/>
-        <v>0.36080269737417053</v>
+        <v>0.35983555959176322</v>
       </c>
       <c r="BP55" s="3">
         <f t="shared" si="17"/>
@@ -13109,14 +13109,14 @@
       <c r="U59" s="15"/>
       <c r="V59" s="3"/>
       <c r="W59" s="7">
-        <v>21.1</v>
+        <v>13.5</v>
       </c>
       <c r="X59" s="3">
         <v>11.781655811736277</v>
       </c>
       <c r="Y59" s="4">
         <f t="shared" si="7"/>
-        <v>0.55837231335243021</v>
+        <v>0.87271524531379829</v>
       </c>
       <c r="Z59" s="3">
         <v>99000.000000000015</v>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="BM59" s="17">
         <f t="shared" si="20"/>
-        <v>25.1</v>
+        <v>17.5</v>
       </c>
       <c r="BN59" s="17">
         <f t="shared" si="20"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="BO59" s="4">
         <f t="shared" si="11"/>
-        <v>0.25733226882826032</v>
+        <v>0.36908799700510481</v>
       </c>
       <c r="BP59" s="3">
         <f t="shared" si="17"/>
@@ -13305,14 +13305,14 @@
       <c r="U60" s="15"/>
       <c r="V60" s="3"/>
       <c r="W60" s="7">
-        <v>25.956</v>
+        <v>26.375999999999998</v>
       </c>
       <c r="X60" s="3">
         <v>17.842736866128618</v>
       </c>
       <c r="Y60" s="4">
         <f t="shared" si="7"/>
-        <v>0.6874224405196725</v>
+        <v>0.67647622331394519</v>
       </c>
       <c r="Z60" s="3">
         <v>99000.000000000015</v>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BM60" s="17">
         <f t="shared" si="20"/>
-        <v>81.236000000000004</v>
+        <v>81.656000000000006</v>
       </c>
       <c r="BN60" s="17">
         <f t="shared" si="20"/>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="BO60" s="4">
         <f t="shared" si="11"/>
-        <v>0.59162334244450698</v>
+        <v>0.58858031065472183</v>
       </c>
       <c r="BP60" s="3">
         <f t="shared" si="17"/>
@@ -13629,14 +13629,14 @@
       </c>
       <c r="V62" s="18"/>
       <c r="W62" s="7">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="X62" s="3">
         <v>35.450044634981815</v>
       </c>
       <c r="Y62" s="4">
         <f t="shared" si="7"/>
-        <v>0.7400844391436705</v>
+        <v>0.73854259656212118</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="BM62" s="17">
         <f>W62+AK62+AY62+I62</f>
-        <v>74.978999999999999</v>
+        <v>75.079000000000008</v>
       </c>
       <c r="BN62" s="17">
         <f>X62+AL62+AZ62+J62</f>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="BO62" s="4">
         <f t="shared" si="11"/>
-        <v>0.6855715932398041</v>
+        <v>0.68465845961623439</v>
       </c>
       <c r="BP62" s="3">
         <f t="shared" si="17"/>
@@ -13905,214 +13905,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:201" x14ac:dyDescent="0.35">
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="W1" s="38" t="s">
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="W1" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
-      <c r="AJ1" s="39"/>
-      <c r="AL1" s="37" t="s">
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AL1" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="AM1" s="37"/>
-      <c r="AN1" s="37"/>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="37"/>
-      <c r="AS1" s="37"/>
-      <c r="AT1" s="37"/>
-      <c r="AU1" s="37"/>
-      <c r="AV1" s="37"/>
-      <c r="AW1" s="37"/>
-      <c r="AX1" s="37"/>
-      <c r="AY1" s="37"/>
-      <c r="BA1" s="37" t="s">
+      <c r="AM1" s="38"/>
+      <c r="AN1" s="38"/>
+      <c r="AO1" s="38"/>
+      <c r="AP1" s="38"/>
+      <c r="AQ1" s="38"/>
+      <c r="AR1" s="38"/>
+      <c r="AS1" s="38"/>
+      <c r="AT1" s="38"/>
+      <c r="AU1" s="38"/>
+      <c r="AV1" s="38"/>
+      <c r="AW1" s="38"/>
+      <c r="AX1" s="38"/>
+      <c r="AY1" s="38"/>
+      <c r="BA1" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="BB1" s="37"/>
-      <c r="BC1" s="37"/>
-      <c r="BD1" s="37"/>
-      <c r="BE1" s="37"/>
-      <c r="BF1" s="37"/>
-      <c r="BG1" s="37"/>
-      <c r="BH1" s="37"/>
-      <c r="BI1" s="37"/>
-      <c r="BJ1" s="37"/>
-      <c r="BK1" s="37"/>
-      <c r="BL1" s="37"/>
-      <c r="BM1" s="37"/>
-      <c r="BN1" s="37"/>
-      <c r="BP1" s="37" t="s">
+      <c r="BB1" s="38"/>
+      <c r="BC1" s="38"/>
+      <c r="BD1" s="38"/>
+      <c r="BE1" s="38"/>
+      <c r="BF1" s="38"/>
+      <c r="BG1" s="38"/>
+      <c r="BH1" s="38"/>
+      <c r="BI1" s="38"/>
+      <c r="BJ1" s="38"/>
+      <c r="BK1" s="38"/>
+      <c r="BL1" s="38"/>
+      <c r="BM1" s="38"/>
+      <c r="BN1" s="38"/>
+      <c r="BP1" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="BQ1" s="37"/>
-      <c r="BR1" s="37"/>
-      <c r="BS1" s="37"/>
-      <c r="BT1" s="37"/>
-      <c r="BU1" s="37"/>
-      <c r="BV1" s="37"/>
-      <c r="BW1" s="37"/>
-      <c r="BX1" s="37"/>
-      <c r="BY1" s="37"/>
-      <c r="BZ1" s="37"/>
-      <c r="CA1" s="37"/>
-      <c r="CB1" s="37"/>
-      <c r="CC1" s="37"/>
-      <c r="CE1" s="37" t="s">
+      <c r="BQ1" s="38"/>
+      <c r="BR1" s="38"/>
+      <c r="BS1" s="38"/>
+      <c r="BT1" s="38"/>
+      <c r="BU1" s="38"/>
+      <c r="BV1" s="38"/>
+      <c r="BW1" s="38"/>
+      <c r="BX1" s="38"/>
+      <c r="BY1" s="38"/>
+      <c r="BZ1" s="38"/>
+      <c r="CA1" s="38"/>
+      <c r="CB1" s="38"/>
+      <c r="CC1" s="38"/>
+      <c r="CE1" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="CF1" s="37"/>
-      <c r="CG1" s="37"/>
-      <c r="CH1" s="37"/>
-      <c r="CI1" s="37"/>
-      <c r="CJ1" s="37"/>
-      <c r="CK1" s="37"/>
-      <c r="CL1" s="37"/>
-      <c r="CM1" s="37"/>
-      <c r="CN1" s="37"/>
-      <c r="CO1" s="37"/>
-      <c r="CP1" s="37"/>
-      <c r="CQ1" s="37"/>
-      <c r="CR1" s="37"/>
-      <c r="CT1" s="37" t="s">
+      <c r="CF1" s="38"/>
+      <c r="CG1" s="38"/>
+      <c r="CH1" s="38"/>
+      <c r="CI1" s="38"/>
+      <c r="CJ1" s="38"/>
+      <c r="CK1" s="38"/>
+      <c r="CL1" s="38"/>
+      <c r="CM1" s="38"/>
+      <c r="CN1" s="38"/>
+      <c r="CO1" s="38"/>
+      <c r="CP1" s="38"/>
+      <c r="CQ1" s="38"/>
+      <c r="CR1" s="38"/>
+      <c r="CT1" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="CU1" s="37"/>
-      <c r="CV1" s="37"/>
-      <c r="CW1" s="37"/>
-      <c r="CX1" s="37"/>
-      <c r="CY1" s="37"/>
-      <c r="CZ1" s="37"/>
-      <c r="DA1" s="37"/>
-      <c r="DB1" s="37"/>
-      <c r="DC1" s="37"/>
-      <c r="DD1" s="37"/>
-      <c r="DE1" s="37"/>
-      <c r="DF1" s="37"/>
-      <c r="DG1" s="37"/>
-      <c r="DI1" s="37" t="s">
+      <c r="CU1" s="38"/>
+      <c r="CV1" s="38"/>
+      <c r="CW1" s="38"/>
+      <c r="CX1" s="38"/>
+      <c r="CY1" s="38"/>
+      <c r="CZ1" s="38"/>
+      <c r="DA1" s="38"/>
+      <c r="DB1" s="38"/>
+      <c r="DC1" s="38"/>
+      <c r="DD1" s="38"/>
+      <c r="DE1" s="38"/>
+      <c r="DF1" s="38"/>
+      <c r="DG1" s="38"/>
+      <c r="DI1" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="DJ1" s="37"/>
-      <c r="DK1" s="37"/>
-      <c r="DL1" s="37"/>
-      <c r="DM1" s="37"/>
-      <c r="DN1" s="37"/>
-      <c r="DO1" s="37"/>
-      <c r="DP1" s="37"/>
-      <c r="DQ1" s="37"/>
-      <c r="DR1" s="37"/>
-      <c r="DS1" s="37"/>
-      <c r="DT1" s="37"/>
-      <c r="DU1" s="37"/>
-      <c r="DV1" s="37"/>
-      <c r="DX1" s="37" t="s">
+      <c r="DJ1" s="38"/>
+      <c r="DK1" s="38"/>
+      <c r="DL1" s="38"/>
+      <c r="DM1" s="38"/>
+      <c r="DN1" s="38"/>
+      <c r="DO1" s="38"/>
+      <c r="DP1" s="38"/>
+      <c r="DQ1" s="38"/>
+      <c r="DR1" s="38"/>
+      <c r="DS1" s="38"/>
+      <c r="DT1" s="38"/>
+      <c r="DU1" s="38"/>
+      <c r="DV1" s="38"/>
+      <c r="DX1" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="DY1" s="37"/>
-      <c r="DZ1" s="37"/>
-      <c r="EA1" s="37"/>
-      <c r="EB1" s="37"/>
-      <c r="EC1" s="37"/>
-      <c r="ED1" s="37"/>
-      <c r="EE1" s="37"/>
-      <c r="EF1" s="37"/>
-      <c r="EG1" s="37"/>
-      <c r="EH1" s="37"/>
-      <c r="EI1" s="37"/>
-      <c r="EJ1" s="37"/>
-      <c r="EK1" s="37"/>
-      <c r="EM1" s="37" t="s">
+      <c r="DY1" s="38"/>
+      <c r="DZ1" s="38"/>
+      <c r="EA1" s="38"/>
+      <c r="EB1" s="38"/>
+      <c r="EC1" s="38"/>
+      <c r="ED1" s="38"/>
+      <c r="EE1" s="38"/>
+      <c r="EF1" s="38"/>
+      <c r="EG1" s="38"/>
+      <c r="EH1" s="38"/>
+      <c r="EI1" s="38"/>
+      <c r="EJ1" s="38"/>
+      <c r="EK1" s="38"/>
+      <c r="EM1" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="EN1" s="37"/>
-      <c r="EO1" s="37"/>
-      <c r="EP1" s="37"/>
-      <c r="EQ1" s="37"/>
-      <c r="ER1" s="37"/>
-      <c r="ES1" s="37"/>
-      <c r="ET1" s="37"/>
-      <c r="EU1" s="37"/>
-      <c r="EV1" s="37"/>
-      <c r="EW1" s="37"/>
-      <c r="EX1" s="37"/>
-      <c r="EY1" s="37"/>
-      <c r="EZ1" s="37"/>
-      <c r="FB1" s="37" t="s">
+      <c r="EN1" s="38"/>
+      <c r="EO1" s="38"/>
+      <c r="EP1" s="38"/>
+      <c r="EQ1" s="38"/>
+      <c r="ER1" s="38"/>
+      <c r="ES1" s="38"/>
+      <c r="ET1" s="38"/>
+      <c r="EU1" s="38"/>
+      <c r="EV1" s="38"/>
+      <c r="EW1" s="38"/>
+      <c r="EX1" s="38"/>
+      <c r="EY1" s="38"/>
+      <c r="EZ1" s="38"/>
+      <c r="FB1" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="FC1" s="37"/>
-      <c r="FD1" s="37"/>
-      <c r="FE1" s="37"/>
-      <c r="FF1" s="37"/>
-      <c r="FG1" s="37"/>
-      <c r="FH1" s="37"/>
-      <c r="FI1" s="37"/>
-      <c r="FJ1" s="37"/>
-      <c r="FK1" s="37"/>
-      <c r="FL1" s="37"/>
-      <c r="FM1" s="37"/>
-      <c r="FN1" s="37"/>
-      <c r="FO1" s="37"/>
-      <c r="FQ1" s="37" t="s">
+      <c r="FC1" s="38"/>
+      <c r="FD1" s="38"/>
+      <c r="FE1" s="38"/>
+      <c r="FF1" s="38"/>
+      <c r="FG1" s="38"/>
+      <c r="FH1" s="38"/>
+      <c r="FI1" s="38"/>
+      <c r="FJ1" s="38"/>
+      <c r="FK1" s="38"/>
+      <c r="FL1" s="38"/>
+      <c r="FM1" s="38"/>
+      <c r="FN1" s="38"/>
+      <c r="FO1" s="38"/>
+      <c r="FQ1" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="FR1" s="37"/>
-      <c r="FS1" s="37"/>
-      <c r="FT1" s="37"/>
-      <c r="FU1" s="37"/>
-      <c r="FV1" s="37"/>
-      <c r="FW1" s="37"/>
-      <c r="FX1" s="37"/>
-      <c r="FY1" s="37"/>
-      <c r="FZ1" s="37"/>
-      <c r="GA1" s="37"/>
-      <c r="GB1" s="37"/>
-      <c r="GC1" s="37"/>
-      <c r="GD1" s="37"/>
-      <c r="GF1" s="37" t="s">
+      <c r="FR1" s="38"/>
+      <c r="FS1" s="38"/>
+      <c r="FT1" s="38"/>
+      <c r="FU1" s="38"/>
+      <c r="FV1" s="38"/>
+      <c r="FW1" s="38"/>
+      <c r="FX1" s="38"/>
+      <c r="FY1" s="38"/>
+      <c r="FZ1" s="38"/>
+      <c r="GA1" s="38"/>
+      <c r="GB1" s="38"/>
+      <c r="GC1" s="38"/>
+      <c r="GD1" s="38"/>
+      <c r="GF1" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="GG1" s="37"/>
-      <c r="GH1" s="37"/>
-      <c r="GI1" s="37"/>
-      <c r="GJ1" s="37"/>
-      <c r="GK1" s="37"/>
-      <c r="GL1" s="37"/>
-      <c r="GM1" s="37"/>
-      <c r="GN1" s="37"/>
-      <c r="GO1" s="37"/>
-      <c r="GP1" s="37"/>
-      <c r="GQ1" s="37"/>
-      <c r="GR1" s="37"/>
-      <c r="GS1" s="37"/>
+      <c r="GG1" s="38"/>
+      <c r="GH1" s="38"/>
+      <c r="GI1" s="38"/>
+      <c r="GJ1" s="38"/>
+      <c r="GK1" s="38"/>
+      <c r="GL1" s="38"/>
+      <c r="GM1" s="38"/>
+      <c r="GN1" s="38"/>
+      <c r="GO1" s="38"/>
+      <c r="GP1" s="38"/>
+      <c r="GQ1" s="38"/>
+      <c r="GR1" s="38"/>
+      <c r="GS1" s="38"/>
     </row>
     <row r="2" spans="1:201" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -35021,6 +35021,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="H1:U1"/>
+    <mergeCell ref="W1:AJ1"/>
+    <mergeCell ref="AL1:AY1"/>
+    <mergeCell ref="BA1:BN1"/>
+    <mergeCell ref="BP1:CC1"/>
     <mergeCell ref="FB1:FO1"/>
     <mergeCell ref="FQ1:GD1"/>
     <mergeCell ref="GF1:GS1"/>
@@ -35029,11 +35034,6 @@
     <mergeCell ref="DI1:DV1"/>
     <mergeCell ref="DX1:EK1"/>
     <mergeCell ref="EM1:EZ1"/>
-    <mergeCell ref="H1:U1"/>
-    <mergeCell ref="W1:AJ1"/>
-    <mergeCell ref="AL1:AY1"/>
-    <mergeCell ref="BA1:BN1"/>
-    <mergeCell ref="BP1:CC1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:B64">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
@@ -35057,34 +35057,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="U1" s="42" t="s">
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="U1" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="42"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4018" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{091CACB0-5A15-4E95-905F-F25101156AC3}"/>
+  <xr:revisionPtr revIDLastSave="4027" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1074916F-9F6D-47A7-B2D3-5DF53747075A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
@@ -791,9 +791,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -807,6 +804,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1217,86 +1217,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.35">
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="V1" s="41" t="s">
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="V1" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="42"/>
-      <c r="AH1" s="42"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AJ1" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-      <c r="AO1" s="40"/>
-      <c r="AP1" s="40"/>
-      <c r="AQ1" s="40"/>
-      <c r="AR1" s="40"/>
-      <c r="AS1" s="40"/>
-      <c r="AT1" s="40"/>
-      <c r="AU1" s="40"/>
-      <c r="AV1" s="40"/>
-      <c r="AX1" s="41" t="s">
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="39"/>
+      <c r="AV1" s="39"/>
+      <c r="AX1" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="AY1" s="42"/>
-      <c r="AZ1" s="42"/>
-      <c r="BA1" s="42"/>
-      <c r="BB1" s="42"/>
-      <c r="BC1" s="42"/>
-      <c r="BD1" s="42"/>
-      <c r="BE1" s="42"/>
-      <c r="BF1" s="42"/>
-      <c r="BG1" s="42"/>
-      <c r="BH1" s="42"/>
-      <c r="BI1" s="42"/>
-      <c r="BJ1" s="42"/>
-      <c r="BL1" s="40" t="s">
+      <c r="AY1" s="41"/>
+      <c r="AZ1" s="41"/>
+      <c r="BA1" s="41"/>
+      <c r="BB1" s="41"/>
+      <c r="BC1" s="41"/>
+      <c r="BD1" s="41"/>
+      <c r="BE1" s="41"/>
+      <c r="BF1" s="41"/>
+      <c r="BG1" s="41"/>
+      <c r="BH1" s="41"/>
+      <c r="BI1" s="41"/>
+      <c r="BJ1" s="41"/>
+      <c r="BL1" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="BM1" s="40"/>
-      <c r="BN1" s="40"/>
-      <c r="BO1" s="40"/>
-      <c r="BP1" s="40"/>
-      <c r="BQ1" s="40"/>
-      <c r="BR1" s="40"/>
-      <c r="BS1" s="40"/>
-      <c r="BT1" s="40"/>
-      <c r="BU1" s="40"/>
-      <c r="BV1" s="40"/>
-      <c r="BW1" s="40"/>
-      <c r="BX1" s="40"/>
-      <c r="BZ1" s="38" t="s">
+      <c r="BM1" s="39"/>
+      <c r="BN1" s="39"/>
+      <c r="BO1" s="39"/>
+      <c r="BP1" s="39"/>
+      <c r="BQ1" s="39"/>
+      <c r="BR1" s="39"/>
+      <c r="BS1" s="39"/>
+      <c r="BT1" s="39"/>
+      <c r="BU1" s="39"/>
+      <c r="BV1" s="39"/>
+      <c r="BW1" s="39"/>
+      <c r="BX1" s="39"/>
+      <c r="BZ1" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="CA1" s="38"/>
-      <c r="CB1" s="38"/>
+      <c r="CA1" s="37"/>
+      <c r="CB1" s="37"/>
       <c r="CD1" s="19" t="s">
         <v>78</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>140</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E35" s="24" t="s">
         <v>106</v>
@@ -10665,7 +10665,7 @@
         <v>140</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E47" s="24" t="s">
         <v>106</v>
@@ -11908,7 +11908,7 @@
         <v>140</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E53" s="25" t="s">
         <v>106</v>
@@ -13905,214 +13905,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:201" x14ac:dyDescent="0.35">
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="W1" s="39" t="s">
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="W1" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AL1" s="38" t="s">
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="39"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
+      <c r="AH1" s="39"/>
+      <c r="AI1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AL1" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="38"/>
-      <c r="AP1" s="38"/>
-      <c r="AQ1" s="38"/>
-      <c r="AR1" s="38"/>
-      <c r="AS1" s="38"/>
-      <c r="AT1" s="38"/>
-      <c r="AU1" s="38"/>
-      <c r="AV1" s="38"/>
-      <c r="AW1" s="38"/>
-      <c r="AX1" s="38"/>
-      <c r="AY1" s="38"/>
-      <c r="BA1" s="38" t="s">
+      <c r="AM1" s="37"/>
+      <c r="AN1" s="37"/>
+      <c r="AO1" s="37"/>
+      <c r="AP1" s="37"/>
+      <c r="AQ1" s="37"/>
+      <c r="AR1" s="37"/>
+      <c r="AS1" s="37"/>
+      <c r="AT1" s="37"/>
+      <c r="AU1" s="37"/>
+      <c r="AV1" s="37"/>
+      <c r="AW1" s="37"/>
+      <c r="AX1" s="37"/>
+      <c r="AY1" s="37"/>
+      <c r="BA1" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="BB1" s="38"/>
-      <c r="BC1" s="38"/>
-      <c r="BD1" s="38"/>
-      <c r="BE1" s="38"/>
-      <c r="BF1" s="38"/>
-      <c r="BG1" s="38"/>
-      <c r="BH1" s="38"/>
-      <c r="BI1" s="38"/>
-      <c r="BJ1" s="38"/>
-      <c r="BK1" s="38"/>
-      <c r="BL1" s="38"/>
-      <c r="BM1" s="38"/>
-      <c r="BN1" s="38"/>
-      <c r="BP1" s="38" t="s">
+      <c r="BB1" s="37"/>
+      <c r="BC1" s="37"/>
+      <c r="BD1" s="37"/>
+      <c r="BE1" s="37"/>
+      <c r="BF1" s="37"/>
+      <c r="BG1" s="37"/>
+      <c r="BH1" s="37"/>
+      <c r="BI1" s="37"/>
+      <c r="BJ1" s="37"/>
+      <c r="BK1" s="37"/>
+      <c r="BL1" s="37"/>
+      <c r="BM1" s="37"/>
+      <c r="BN1" s="37"/>
+      <c r="BP1" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="BQ1" s="38"/>
-      <c r="BR1" s="38"/>
-      <c r="BS1" s="38"/>
-      <c r="BT1" s="38"/>
-      <c r="BU1" s="38"/>
-      <c r="BV1" s="38"/>
-      <c r="BW1" s="38"/>
-      <c r="BX1" s="38"/>
-      <c r="BY1" s="38"/>
-      <c r="BZ1" s="38"/>
-      <c r="CA1" s="38"/>
-      <c r="CB1" s="38"/>
-      <c r="CC1" s="38"/>
-      <c r="CE1" s="38" t="s">
+      <c r="BQ1" s="37"/>
+      <c r="BR1" s="37"/>
+      <c r="BS1" s="37"/>
+      <c r="BT1" s="37"/>
+      <c r="BU1" s="37"/>
+      <c r="BV1" s="37"/>
+      <c r="BW1" s="37"/>
+      <c r="BX1" s="37"/>
+      <c r="BY1" s="37"/>
+      <c r="BZ1" s="37"/>
+      <c r="CA1" s="37"/>
+      <c r="CB1" s="37"/>
+      <c r="CC1" s="37"/>
+      <c r="CE1" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="CF1" s="38"/>
-      <c r="CG1" s="38"/>
-      <c r="CH1" s="38"/>
-      <c r="CI1" s="38"/>
-      <c r="CJ1" s="38"/>
-      <c r="CK1" s="38"/>
-      <c r="CL1" s="38"/>
-      <c r="CM1" s="38"/>
-      <c r="CN1" s="38"/>
-      <c r="CO1" s="38"/>
-      <c r="CP1" s="38"/>
-      <c r="CQ1" s="38"/>
-      <c r="CR1" s="38"/>
-      <c r="CT1" s="38" t="s">
+      <c r="CF1" s="37"/>
+      <c r="CG1" s="37"/>
+      <c r="CH1" s="37"/>
+      <c r="CI1" s="37"/>
+      <c r="CJ1" s="37"/>
+      <c r="CK1" s="37"/>
+      <c r="CL1" s="37"/>
+      <c r="CM1" s="37"/>
+      <c r="CN1" s="37"/>
+      <c r="CO1" s="37"/>
+      <c r="CP1" s="37"/>
+      <c r="CQ1" s="37"/>
+      <c r="CR1" s="37"/>
+      <c r="CT1" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="CU1" s="38"/>
-      <c r="CV1" s="38"/>
-      <c r="CW1" s="38"/>
-      <c r="CX1" s="38"/>
-      <c r="CY1" s="38"/>
-      <c r="CZ1" s="38"/>
-      <c r="DA1" s="38"/>
-      <c r="DB1" s="38"/>
-      <c r="DC1" s="38"/>
-      <c r="DD1" s="38"/>
-      <c r="DE1" s="38"/>
-      <c r="DF1" s="38"/>
-      <c r="DG1" s="38"/>
-      <c r="DI1" s="38" t="s">
+      <c r="CU1" s="37"/>
+      <c r="CV1" s="37"/>
+      <c r="CW1" s="37"/>
+      <c r="CX1" s="37"/>
+      <c r="CY1" s="37"/>
+      <c r="CZ1" s="37"/>
+      <c r="DA1" s="37"/>
+      <c r="DB1" s="37"/>
+      <c r="DC1" s="37"/>
+      <c r="DD1" s="37"/>
+      <c r="DE1" s="37"/>
+      <c r="DF1" s="37"/>
+      <c r="DG1" s="37"/>
+      <c r="DI1" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="DJ1" s="38"/>
-      <c r="DK1" s="38"/>
-      <c r="DL1" s="38"/>
-      <c r="DM1" s="38"/>
-      <c r="DN1" s="38"/>
-      <c r="DO1" s="38"/>
-      <c r="DP1" s="38"/>
-      <c r="DQ1" s="38"/>
-      <c r="DR1" s="38"/>
-      <c r="DS1" s="38"/>
-      <c r="DT1" s="38"/>
-      <c r="DU1" s="38"/>
-      <c r="DV1" s="38"/>
-      <c r="DX1" s="38" t="s">
+      <c r="DJ1" s="37"/>
+      <c r="DK1" s="37"/>
+      <c r="DL1" s="37"/>
+      <c r="DM1" s="37"/>
+      <c r="DN1" s="37"/>
+      <c r="DO1" s="37"/>
+      <c r="DP1" s="37"/>
+      <c r="DQ1" s="37"/>
+      <c r="DR1" s="37"/>
+      <c r="DS1" s="37"/>
+      <c r="DT1" s="37"/>
+      <c r="DU1" s="37"/>
+      <c r="DV1" s="37"/>
+      <c r="DX1" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="DY1" s="38"/>
-      <c r="DZ1" s="38"/>
-      <c r="EA1" s="38"/>
-      <c r="EB1" s="38"/>
-      <c r="EC1" s="38"/>
-      <c r="ED1" s="38"/>
-      <c r="EE1" s="38"/>
-      <c r="EF1" s="38"/>
-      <c r="EG1" s="38"/>
-      <c r="EH1" s="38"/>
-      <c r="EI1" s="38"/>
-      <c r="EJ1" s="38"/>
-      <c r="EK1" s="38"/>
-      <c r="EM1" s="38" t="s">
+      <c r="DY1" s="37"/>
+      <c r="DZ1" s="37"/>
+      <c r="EA1" s="37"/>
+      <c r="EB1" s="37"/>
+      <c r="EC1" s="37"/>
+      <c r="ED1" s="37"/>
+      <c r="EE1" s="37"/>
+      <c r="EF1" s="37"/>
+      <c r="EG1" s="37"/>
+      <c r="EH1" s="37"/>
+      <c r="EI1" s="37"/>
+      <c r="EJ1" s="37"/>
+      <c r="EK1" s="37"/>
+      <c r="EM1" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="EN1" s="38"/>
-      <c r="EO1" s="38"/>
-      <c r="EP1" s="38"/>
-      <c r="EQ1" s="38"/>
-      <c r="ER1" s="38"/>
-      <c r="ES1" s="38"/>
-      <c r="ET1" s="38"/>
-      <c r="EU1" s="38"/>
-      <c r="EV1" s="38"/>
-      <c r="EW1" s="38"/>
-      <c r="EX1" s="38"/>
-      <c r="EY1" s="38"/>
-      <c r="EZ1" s="38"/>
-      <c r="FB1" s="38" t="s">
+      <c r="EN1" s="37"/>
+      <c r="EO1" s="37"/>
+      <c r="EP1" s="37"/>
+      <c r="EQ1" s="37"/>
+      <c r="ER1" s="37"/>
+      <c r="ES1" s="37"/>
+      <c r="ET1" s="37"/>
+      <c r="EU1" s="37"/>
+      <c r="EV1" s="37"/>
+      <c r="EW1" s="37"/>
+      <c r="EX1" s="37"/>
+      <c r="EY1" s="37"/>
+      <c r="EZ1" s="37"/>
+      <c r="FB1" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="FC1" s="38"/>
-      <c r="FD1" s="38"/>
-      <c r="FE1" s="38"/>
-      <c r="FF1" s="38"/>
-      <c r="FG1" s="38"/>
-      <c r="FH1" s="38"/>
-      <c r="FI1" s="38"/>
-      <c r="FJ1" s="38"/>
-      <c r="FK1" s="38"/>
-      <c r="FL1" s="38"/>
-      <c r="FM1" s="38"/>
-      <c r="FN1" s="38"/>
-      <c r="FO1" s="38"/>
-      <c r="FQ1" s="38" t="s">
+      <c r="FC1" s="37"/>
+      <c r="FD1" s="37"/>
+      <c r="FE1" s="37"/>
+      <c r="FF1" s="37"/>
+      <c r="FG1" s="37"/>
+      <c r="FH1" s="37"/>
+      <c r="FI1" s="37"/>
+      <c r="FJ1" s="37"/>
+      <c r="FK1" s="37"/>
+      <c r="FL1" s="37"/>
+      <c r="FM1" s="37"/>
+      <c r="FN1" s="37"/>
+      <c r="FO1" s="37"/>
+      <c r="FQ1" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="FR1" s="38"/>
-      <c r="FS1" s="38"/>
-      <c r="FT1" s="38"/>
-      <c r="FU1" s="38"/>
-      <c r="FV1" s="38"/>
-      <c r="FW1" s="38"/>
-      <c r="FX1" s="38"/>
-      <c r="FY1" s="38"/>
-      <c r="FZ1" s="38"/>
-      <c r="GA1" s="38"/>
-      <c r="GB1" s="38"/>
-      <c r="GC1" s="38"/>
-      <c r="GD1" s="38"/>
-      <c r="GF1" s="38" t="s">
+      <c r="FR1" s="37"/>
+      <c r="FS1" s="37"/>
+      <c r="FT1" s="37"/>
+      <c r="FU1" s="37"/>
+      <c r="FV1" s="37"/>
+      <c r="FW1" s="37"/>
+      <c r="FX1" s="37"/>
+      <c r="FY1" s="37"/>
+      <c r="FZ1" s="37"/>
+      <c r="GA1" s="37"/>
+      <c r="GB1" s="37"/>
+      <c r="GC1" s="37"/>
+      <c r="GD1" s="37"/>
+      <c r="GF1" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="GG1" s="38"/>
-      <c r="GH1" s="38"/>
-      <c r="GI1" s="38"/>
-      <c r="GJ1" s="38"/>
-      <c r="GK1" s="38"/>
-      <c r="GL1" s="38"/>
-      <c r="GM1" s="38"/>
-      <c r="GN1" s="38"/>
-      <c r="GO1" s="38"/>
-      <c r="GP1" s="38"/>
-      <c r="GQ1" s="38"/>
-      <c r="GR1" s="38"/>
-      <c r="GS1" s="38"/>
+      <c r="GG1" s="37"/>
+      <c r="GH1" s="37"/>
+      <c r="GI1" s="37"/>
+      <c r="GJ1" s="37"/>
+      <c r="GK1" s="37"/>
+      <c r="GL1" s="37"/>
+      <c r="GM1" s="37"/>
+      <c r="GN1" s="37"/>
+      <c r="GO1" s="37"/>
+      <c r="GP1" s="37"/>
+      <c r="GQ1" s="37"/>
+      <c r="GR1" s="37"/>
+      <c r="GS1" s="37"/>
     </row>
     <row r="2" spans="1:201" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -35021,11 +35021,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="H1:U1"/>
-    <mergeCell ref="W1:AJ1"/>
-    <mergeCell ref="AL1:AY1"/>
-    <mergeCell ref="BA1:BN1"/>
-    <mergeCell ref="BP1:CC1"/>
     <mergeCell ref="FB1:FO1"/>
     <mergeCell ref="FQ1:GD1"/>
     <mergeCell ref="GF1:GS1"/>
@@ -35034,6 +35029,11 @@
     <mergeCell ref="DI1:DV1"/>
     <mergeCell ref="DX1:EK1"/>
     <mergeCell ref="EM1:EZ1"/>
+    <mergeCell ref="H1:U1"/>
+    <mergeCell ref="W1:AJ1"/>
+    <mergeCell ref="AL1:AY1"/>
+    <mergeCell ref="BA1:BN1"/>
+    <mergeCell ref="BP1:CC1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:B64">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
@@ -35057,34 +35057,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="U1" s="37" t="s">
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="U1" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
+      <c r="AD1" s="42"/>
+      <c r="AE1" s="42"/>
+      <c r="AF1" s="42"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">

--- a/CEO Review.xlsx
+++ b/CEO Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peoplestronghrservices-my.sharepoint.com/personal/baljeet_singh_taggd_in/Documents/Desktop/Clude Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4027" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1074916F-9F6D-47A7-B2D3-5DF53747075A}"/>
+  <xr:revisionPtr revIDLastSave="4049" documentId="8_{231760F8-40C3-4E52-9138-CD9DD8E2170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{314254D1-01A1-43D5-A146-D4119FBDE362}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{F2C8E0B5-D69E-42FC-A0A4-20379F29D696}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="Collection Detail" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$F$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Collection Detail'!$A$2:$F$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$CP$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Actual!$A$2:$GS$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Collection Detail'!$A$2:$AF$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$F$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -8208,7 +8208,7 @@
         <v>106</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="14">
@@ -10671,7 +10671,7 @@
         <v>106</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="14">
@@ -11914,7 +11914,7 @@
         <v>106</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="14">
@@ -25242,13 +25242,13 @@
         <v>140</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G35" s="18"/>
       <c r="H35" s="14">
@@ -29196,13 +29196,13 @@
         <v>140</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G47" s="18"/>
       <c r="H47" s="14">
@@ -31178,13 +31178,13 @@
         <v>140</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G53" s="18"/>
       <c r="H53" s="14">
@@ -35021,6 +35021,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="H1:U1"/>
+    <mergeCell ref="W1:AJ1"/>
+    <mergeCell ref="AL1:AY1"/>
+    <mergeCell ref="BA1:BN1"/>
+    <mergeCell ref="BP1:CC1"/>
     <mergeCell ref="FB1:FO1"/>
     <mergeCell ref="FQ1:GD1"/>
     <mergeCell ref="GF1:GS1"/>
@@ -35029,11 +35034,6 @@
     <mergeCell ref="DI1:DV1"/>
     <mergeCell ref="DX1:EK1"/>
     <mergeCell ref="EM1:EZ1"/>
-    <mergeCell ref="H1:U1"/>
-    <mergeCell ref="W1:AJ1"/>
-    <mergeCell ref="AL1:AY1"/>
-    <mergeCell ref="BA1:BN1"/>
-    <mergeCell ref="BP1:CC1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:B64">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
@@ -36405,13 +36405,13 @@
         <v>140</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -36861,13 +36861,13 @@
         <v>140</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -37089,13 +37089,13 @@
         <v>140</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="H53">
         <v>0</v>
